--- a/exp_database/test_JAQOS/output/miappe_template_filled.xlsx
+++ b/exp_database/test_JAQOS/output/miappe_template_filled.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1842" uniqueCount="873">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="614">
   <si>
     <t xml:space="preserve">README</t>
   </si>
@@ -1620,862 +1620,85 @@
     <t xml:space="preserve">valeur</t>
   </si>
   <si>
-    <t xml:space="preserve">opensilex-sandbox:id/experiment/the_jacos_experience</t>
+    <t xml:space="preserve">demo2:id/experiment/the_jacos_experience</t>
   </si>
   <si>
     <t xml:space="preserve">http://opensilex.test/id/germplasm/variety.huachano</t>
   </si>
   <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_53_3</t>
+    <t xml:space="preserve">demo2:id/scientific-object/so-2024_toab_stress_53</t>
   </si>
   <si>
     <t xml:space="preserve">vocabulary:Plant</t>
   </si>
   <si>
-    <t xml:space="preserve">2024_ToAB_Stress_53_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/factor/the_jacos_experience.drough_stress.dr_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04 12:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_54_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_54_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/factor/the_jacos_experience.salt_stress.salt_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_55_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_55_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/factor/the_jacos_experience.salt_stress.salt_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_56_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_56_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_57_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_57_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/factor/the_jacos_experience.optimal_growth.control</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_58_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_58_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/factor/the_jacos_experience.drough_stress.dr_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_59_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_59_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_60_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_60_3</t>
+    <t xml:space="preserve">2024_ToAB_Stress_53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">demo2:id/factor/the_jacos_experience.drough_stress.dr_02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-07 15:21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">demo2:id/scientific-object/so-2024_toab_stress_54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024_ToAB_Stress_54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">demo2:id/factor/the_jacos_experience.salt_stress.salt_02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">demo2:id/scientific-object/so-2024_toab_stress_55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024_ToAB_Stress_55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">demo2:id/factor/the_jacos_experience.salt_stress.salt_01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-07 15:22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">demo2:id/scientific-object/so-2024_toab_stress_56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024_ToAB_Stress_56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">demo2:id/scientific-object/so-2024_toab_stress_57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024_ToAB_Stress_57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">demo2:id/factor/the_jacos_experience.optimal_growth.control</t>
+  </si>
+  <si>
+    <t xml:space="preserve">demo2:id/scientific-object/so-2024_toab_stress_58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024_ToAB_Stress_58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">demo2:id/factor/the_jacos_experience.drough_stress.dr_01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">demo2:id/scientific-object/so-2024_toab_stress_59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024_ToAB_Stress_59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">demo2:id/scientific-object/so-2024_toab_stress_60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024_ToAB_Stress_60</t>
   </si>
   <si>
     <t xml:space="preserve">http://opensilex.test/id/germplasm/variety.tiny_tim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_61_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_61_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_62_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_62_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_63_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_63_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_64_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_64_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_65_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_65_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_66_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_66_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_67_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_67_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04 12:16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_68_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_68_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_69_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_69_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_70_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_70_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_71_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_71_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_72_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_72_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_73_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_73_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_74_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_74_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_75_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_75_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_76_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_76_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_77_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_77_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_78_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_78_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_79_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_79_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_80_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_80_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_81_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_81_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_82_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_82_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/experiment/test_import_image</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_53_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_53_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/factor/test_import_image.drough_stress.high_drought_stress_drought_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04 17:08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_54_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_54_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/factor/test_import_image.salt_stress.high_salt_stress_salt_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_55_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_55_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/factor/test_import_image.salt_stress.medium_salt_stress_salt_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_56_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_56_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_57_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_57_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/factor/test_import_image.optimal_growth.optimal_growth_control</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_58_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_58_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/factor/test_import_image.drough_stress.medium_drought_stress_drought_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_59_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_59_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_60_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_60_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_61_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_61_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_62_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_62_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_63_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_63_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_64_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_64_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_65_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_65_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_66_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_66_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_67_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_67_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_68_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_68_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_69_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_69_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_70_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_70_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_71_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_71_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_72_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_72_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_73_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_73_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_74_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_74_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_75_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_75_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_76_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_76_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_77_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_77_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_78_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_78_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_79_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_79_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_80_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_80_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_81_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_81_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_82_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_82_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_5310</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_5310</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-05 15:32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_5410</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_5410</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_5510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_5510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_5610</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_5610</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_5710</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_5710</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_5810</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_5810</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_5910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_5910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_6010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_6010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_6110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_6110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_6210</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_6210</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_6310</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_6310</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_6410</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_6410</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_6510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_6510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_6610</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_6610</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_6710</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_6710</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_6810</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_6810</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_6910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_6910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_7010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_7010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_7110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_7110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_7210</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_7210</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-05 15:33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_7310</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_7310</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_7410</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_7410</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_7510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_7510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_7610</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_7610</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_7710</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_7710</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_7810</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_7810</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_7910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_7910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_8010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_8010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_8110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_8110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_8210</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_8210</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_53_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_53_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-05 17:01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_54_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_54_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_55_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_55_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_56_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_56_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_57_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_57_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_58_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_58_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_59_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_59_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_60_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_60_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_61_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_61_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_62_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_62_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-05 17:02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_63_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_63_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_64_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_64_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_65_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_65_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_66_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_66_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_67_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_67_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_68_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_68_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_69_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_69_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_70_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_70_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_71_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_71_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_72_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_72_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_73_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_73_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_74_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_74_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_75_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_75_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_76_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_76_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_77_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_77_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_78_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_78_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_79_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_79_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_80_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_80_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_81_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_81_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opensilex-sandbox:id/scientific-object/so-2024_toab_stress_82_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_82_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">demo2:id/experiment/the_jacos_experience</t>
-  </si>
-  <si>
-    <t xml:space="preserve">demo2:id/scientific-object/so-2024_toab_stress_53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">demo2:id/factor/the_jacos_experience.drough_stress.dr_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-07 15:21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">demo2:id/scientific-object/so-2024_toab_stress_54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">demo2:id/factor/the_jacos_experience.salt_stress.salt_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">demo2:id/scientific-object/so-2024_toab_stress_55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">demo2:id/factor/the_jacos_experience.salt_stress.salt_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-07 15:22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">demo2:id/scientific-object/so-2024_toab_stress_56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">demo2:id/scientific-object/so-2024_toab_stress_57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">demo2:id/factor/the_jacos_experience.optimal_growth.control</t>
-  </si>
-  <si>
-    <t xml:space="preserve">demo2:id/scientific-object/so-2024_toab_stress_58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">demo2:id/factor/the_jacos_experience.drough_stress.dr_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">demo2:id/scientific-object/so-2024_toab_stress_59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">demo2:id/scientific-object/so-2024_toab_stress_60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024_ToAB_Stress_60</t>
   </si>
   <si>
     <t xml:space="preserve">demo2:id/scientific-object/so-2024_toab_stress_61</t>
@@ -2993,303 +2216,303 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -13312,17 +12535,17 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H152"/>
+  <dimension ref="A1:H1048576"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="41.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46.74"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="44.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="23.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="34.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="1.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="53.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="17.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="41.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="46.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="44.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="23.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="34.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="1.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="53.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="17.11"/>
   </cols>
   <sheetData>
     <row r="1" s="61" customFormat="true" ht="26.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13352,3505 +12575,865 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" s="1" t="s">
         <v>525</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="62" t="s">
         <v>526</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="63" t="s">
         <v>527</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="64" t="s">
         <v>528</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="65" t="s">
         <v>529</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="66" t="s">
         <v>530</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="F3" s="67"/>
+      <c r="G3" s="68" t="s">
         <v>531</v>
       </c>
-      <c r="H3" s="0" t="s">
+      <c r="H3" s="69" t="s">
         <v>532</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="62" t="s">
         <v>526</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="63" t="s">
         <v>527</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="64" t="s">
         <v>533</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="65" t="s">
         <v>529</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="66" t="s">
         <v>534</v>
       </c>
-      <c r="G4" s="0" t="s">
+      <c r="F4" s="67"/>
+      <c r="G4" s="68" t="s">
         <v>535</v>
       </c>
-      <c r="H4" s="0" t="s">
+      <c r="H4" s="69" t="s">
         <v>532</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="62" t="s">
         <v>526</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="63" t="s">
         <v>527</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="64" t="s">
         <v>536</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="65" t="s">
         <v>529</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="66" t="s">
         <v>537</v>
       </c>
-      <c r="G5" s="0" t="s">
+      <c r="F5" s="67"/>
+      <c r="G5" s="68" t="s">
         <v>538</v>
       </c>
-      <c r="H5" s="0" t="s">
-        <v>532</v>
+      <c r="H5" s="69" t="s">
+        <v>539</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="62" t="s">
         <v>526</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="63" t="s">
         <v>527</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="64" t="s">
+        <v>540</v>
+      </c>
+      <c r="D6" s="65" t="s">
+        <v>529</v>
+      </c>
+      <c r="E6" s="66" t="s">
+        <v>541</v>
+      </c>
+      <c r="F6" s="67"/>
+      <c r="G6" s="68" t="s">
+        <v>535</v>
+      </c>
+      <c r="H6" s="69" t="s">
         <v>539</v>
       </c>
-      <c r="D6" s="0" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="62" t="s">
+        <v>526</v>
+      </c>
+      <c r="B7" s="63" t="s">
+        <v>527</v>
+      </c>
+      <c r="C7" s="64" t="s">
+        <v>542</v>
+      </c>
+      <c r="D7" s="65" t="s">
         <v>529</v>
       </c>
-      <c r="E6" s="0" t="s">
-        <v>540</v>
-      </c>
-      <c r="G6" s="0" t="s">
+      <c r="E7" s="66" t="s">
+        <v>543</v>
+      </c>
+      <c r="F7" s="67"/>
+      <c r="G7" s="68" t="s">
+        <v>544</v>
+      </c>
+      <c r="H7" s="69" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="62" t="s">
+        <v>526</v>
+      </c>
+      <c r="B8" s="63" t="s">
+        <v>527</v>
+      </c>
+      <c r="C8" s="64" t="s">
+        <v>545</v>
+      </c>
+      <c r="D8" s="65" t="s">
+        <v>529</v>
+      </c>
+      <c r="E8" s="66" t="s">
+        <v>546</v>
+      </c>
+      <c r="F8" s="67"/>
+      <c r="G8" s="68" t="s">
+        <v>547</v>
+      </c>
+      <c r="H8" s="69" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="62" t="s">
+        <v>526</v>
+      </c>
+      <c r="B9" s="63" t="s">
+        <v>527</v>
+      </c>
+      <c r="C9" s="64" t="s">
+        <v>548</v>
+      </c>
+      <c r="D9" s="65" t="s">
+        <v>529</v>
+      </c>
+      <c r="E9" s="66" t="s">
+        <v>549</v>
+      </c>
+      <c r="F9" s="67"/>
+      <c r="G9" s="68" t="s">
+        <v>531</v>
+      </c>
+      <c r="H9" s="69" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="62" t="s">
+        <v>526</v>
+      </c>
+      <c r="B10" s="63" t="s">
+        <v>527</v>
+      </c>
+      <c r="C10" s="64" t="s">
+        <v>550</v>
+      </c>
+      <c r="D10" s="65" t="s">
+        <v>529</v>
+      </c>
+      <c r="E10" s="66" t="s">
+        <v>551</v>
+      </c>
+      <c r="F10" s="67"/>
+      <c r="G10" s="68" t="s">
+        <v>544</v>
+      </c>
+      <c r="H10" s="69" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="62" t="s">
+        <v>526</v>
+      </c>
+      <c r="B11" s="63" t="s">
+        <v>552</v>
+      </c>
+      <c r="C11" s="64" t="s">
+        <v>553</v>
+      </c>
+      <c r="D11" s="65" t="s">
+        <v>529</v>
+      </c>
+      <c r="E11" s="66" t="s">
+        <v>554</v>
+      </c>
+      <c r="F11" s="67"/>
+      <c r="G11" s="68" t="s">
+        <v>547</v>
+      </c>
+      <c r="H11" s="69" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="62" t="s">
+        <v>526</v>
+      </c>
+      <c r="B12" s="63" t="s">
+        <v>552</v>
+      </c>
+      <c r="C12" s="64" t="s">
+        <v>555</v>
+      </c>
+      <c r="D12" s="65" t="s">
+        <v>529</v>
+      </c>
+      <c r="E12" s="66" t="s">
+        <v>556</v>
+      </c>
+      <c r="F12" s="67"/>
+      <c r="G12" s="68" t="s">
+        <v>538</v>
+      </c>
+      <c r="H12" s="69" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="62" t="s">
+        <v>526</v>
+      </c>
+      <c r="B13" s="63" t="s">
+        <v>552</v>
+      </c>
+      <c r="C13" s="64" t="s">
+        <v>557</v>
+      </c>
+      <c r="D13" s="65" t="s">
+        <v>529</v>
+      </c>
+      <c r="E13" s="66" t="s">
+        <v>558</v>
+      </c>
+      <c r="F13" s="67"/>
+      <c r="G13" s="68" t="s">
+        <v>538</v>
+      </c>
+      <c r="H13" s="69" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="62" t="s">
+        <v>526</v>
+      </c>
+      <c r="B14" s="63" t="s">
+        <v>552</v>
+      </c>
+      <c r="C14" s="64" t="s">
+        <v>559</v>
+      </c>
+      <c r="D14" s="65" t="s">
+        <v>529</v>
+      </c>
+      <c r="E14" s="66" t="s">
+        <v>560</v>
+      </c>
+      <c r="F14" s="67"/>
+      <c r="G14" s="68" t="s">
+        <v>544</v>
+      </c>
+      <c r="H14" s="69" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="62" t="s">
+        <v>526</v>
+      </c>
+      <c r="B15" s="63" t="s">
+        <v>552</v>
+      </c>
+      <c r="C15" s="64" t="s">
+        <v>561</v>
+      </c>
+      <c r="D15" s="65" t="s">
+        <v>529</v>
+      </c>
+      <c r="E15" s="66" t="s">
+        <v>562</v>
+      </c>
+      <c r="F15" s="67"/>
+      <c r="G15" s="68" t="s">
         <v>535</v>
       </c>
-      <c r="H6" s="0" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="H15" s="69" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="62" t="s">
         <v>526</v>
       </c>
-      <c r="B7" s="0" t="s">
-        <v>527</v>
-      </c>
-      <c r="C7" s="0" t="s">
-        <v>541</v>
-      </c>
-      <c r="D7" s="0" t="s">
+      <c r="B16" s="63" t="s">
+        <v>552</v>
+      </c>
+      <c r="C16" s="64" t="s">
+        <v>563</v>
+      </c>
+      <c r="D16" s="65" t="s">
         <v>529</v>
       </c>
-      <c r="E7" s="0" t="s">
-        <v>542</v>
-      </c>
-      <c r="G7" s="0" t="s">
-        <v>543</v>
-      </c>
-      <c r="H7" s="0" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="E16" s="66" t="s">
+        <v>564</v>
+      </c>
+      <c r="F16" s="67"/>
+      <c r="G16" s="68" t="s">
+        <v>531</v>
+      </c>
+      <c r="H16" s="69" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="62" t="s">
         <v>526</v>
       </c>
-      <c r="B8" s="0" t="s">
-        <v>527</v>
-      </c>
-      <c r="C8" s="0" t="s">
+      <c r="B17" s="63" t="s">
+        <v>552</v>
+      </c>
+      <c r="C17" s="64" t="s">
+        <v>565</v>
+      </c>
+      <c r="D17" s="65" t="s">
+        <v>529</v>
+      </c>
+      <c r="E17" s="66" t="s">
+        <v>566</v>
+      </c>
+      <c r="F17" s="67"/>
+      <c r="G17" s="68" t="s">
+        <v>547</v>
+      </c>
+      <c r="H17" s="69" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="62" t="s">
+        <v>526</v>
+      </c>
+      <c r="B18" s="63" t="s">
+        <v>552</v>
+      </c>
+      <c r="C18" s="64" t="s">
+        <v>567</v>
+      </c>
+      <c r="D18" s="65" t="s">
+        <v>529</v>
+      </c>
+      <c r="E18" s="66" t="s">
+        <v>568</v>
+      </c>
+      <c r="F18" s="67"/>
+      <c r="G18" s="68" t="s">
+        <v>538</v>
+      </c>
+      <c r="H18" s="69" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="62" t="s">
+        <v>526</v>
+      </c>
+      <c r="B19" s="63" t="s">
+        <v>552</v>
+      </c>
+      <c r="C19" s="64" t="s">
+        <v>569</v>
+      </c>
+      <c r="D19" s="65" t="s">
+        <v>529</v>
+      </c>
+      <c r="E19" s="66" t="s">
+        <v>570</v>
+      </c>
+      <c r="F19" s="67"/>
+      <c r="G19" s="68" t="s">
+        <v>547</v>
+      </c>
+      <c r="H19" s="69" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="62" t="s">
+        <v>526</v>
+      </c>
+      <c r="B20" s="63" t="s">
+        <v>552</v>
+      </c>
+      <c r="C20" s="64" t="s">
+        <v>571</v>
+      </c>
+      <c r="D20" s="65" t="s">
+        <v>529</v>
+      </c>
+      <c r="E20" s="66" t="s">
+        <v>572</v>
+      </c>
+      <c r="F20" s="67"/>
+      <c r="G20" s="68" t="s">
+        <v>538</v>
+      </c>
+      <c r="H20" s="69" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="62" t="s">
+        <v>526</v>
+      </c>
+      <c r="B21" s="63" t="s">
+        <v>552</v>
+      </c>
+      <c r="C21" s="64" t="s">
+        <v>573</v>
+      </c>
+      <c r="D21" s="65" t="s">
+        <v>529</v>
+      </c>
+      <c r="E21" s="66" t="s">
+        <v>574</v>
+      </c>
+      <c r="F21" s="67"/>
+      <c r="G21" s="68" t="s">
+        <v>547</v>
+      </c>
+      <c r="H21" s="69" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="62" t="s">
+        <v>526</v>
+      </c>
+      <c r="B22" s="63" t="s">
+        <v>552</v>
+      </c>
+      <c r="C22" s="64" t="s">
+        <v>575</v>
+      </c>
+      <c r="D22" s="65" t="s">
+        <v>529</v>
+      </c>
+      <c r="E22" s="66" t="s">
+        <v>576</v>
+      </c>
+      <c r="F22" s="67"/>
+      <c r="G22" s="68" t="s">
+        <v>535</v>
+      </c>
+      <c r="H22" s="69" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="62" t="s">
+        <v>526</v>
+      </c>
+      <c r="B23" s="63" t="s">
+        <v>552</v>
+      </c>
+      <c r="C23" s="64" t="s">
+        <v>577</v>
+      </c>
+      <c r="D23" s="65" t="s">
+        <v>529</v>
+      </c>
+      <c r="E23" s="66" t="s">
+        <v>578</v>
+      </c>
+      <c r="F23" s="67"/>
+      <c r="G23" s="68" t="s">
+        <v>531</v>
+      </c>
+      <c r="H23" s="69" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="62" t="s">
+        <v>526</v>
+      </c>
+      <c r="B24" s="63" t="s">
+        <v>552</v>
+      </c>
+      <c r="C24" s="64" t="s">
+        <v>579</v>
+      </c>
+      <c r="D24" s="65" t="s">
+        <v>529</v>
+      </c>
+      <c r="E24" s="66" t="s">
+        <v>580</v>
+      </c>
+      <c r="F24" s="67"/>
+      <c r="G24" s="68" t="s">
         <v>544</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="H24" s="69" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="62" t="s">
+        <v>526</v>
+      </c>
+      <c r="B25" s="63" t="s">
+        <v>552</v>
+      </c>
+      <c r="C25" s="64" t="s">
+        <v>581</v>
+      </c>
+      <c r="D25" s="65" t="s">
         <v>529</v>
       </c>
-      <c r="E8" s="0" t="s">
-        <v>545</v>
-      </c>
-      <c r="G8" s="0" t="s">
-        <v>546</v>
-      </c>
-      <c r="H8" s="0" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="E25" s="66" t="s">
+        <v>582</v>
+      </c>
+      <c r="F25" s="67"/>
+      <c r="G25" s="68" t="s">
+        <v>535</v>
+      </c>
+      <c r="H25" s="69" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="62" t="s">
         <v>526</v>
       </c>
-      <c r="B9" s="0" t="s">
-        <v>527</v>
-      </c>
-      <c r="C9" s="0" t="s">
+      <c r="B26" s="63" t="s">
+        <v>552</v>
+      </c>
+      <c r="C26" s="64" t="s">
+        <v>583</v>
+      </c>
+      <c r="D26" s="65" t="s">
+        <v>529</v>
+      </c>
+      <c r="E26" s="66" t="s">
+        <v>584</v>
+      </c>
+      <c r="F26" s="67"/>
+      <c r="G26" s="68" t="s">
         <v>547</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="H26" s="69" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="62" t="s">
+        <v>526</v>
+      </c>
+      <c r="B27" s="63" t="s">
+        <v>552</v>
+      </c>
+      <c r="C27" s="64" t="s">
+        <v>585</v>
+      </c>
+      <c r="D27" s="65" t="s">
         <v>529</v>
       </c>
-      <c r="E9" s="0" t="s">
-        <v>548</v>
-      </c>
-      <c r="G9" s="0" t="s">
+      <c r="E27" s="66" t="s">
+        <v>586</v>
+      </c>
+      <c r="F27" s="67"/>
+      <c r="G27" s="68" t="s">
+        <v>535</v>
+      </c>
+      <c r="H27" s="69" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="62" t="s">
+        <v>526</v>
+      </c>
+      <c r="B28" s="63" t="s">
+        <v>552</v>
+      </c>
+      <c r="C28" s="64" t="s">
+        <v>587</v>
+      </c>
+      <c r="D28" s="65" t="s">
+        <v>529</v>
+      </c>
+      <c r="E28" s="66" t="s">
+        <v>588</v>
+      </c>
+      <c r="F28" s="67"/>
+      <c r="G28" s="68" t="s">
+        <v>538</v>
+      </c>
+      <c r="H28" s="69" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="62" t="s">
+        <v>526</v>
+      </c>
+      <c r="B29" s="63" t="s">
+        <v>552</v>
+      </c>
+      <c r="C29" s="64" t="s">
+        <v>589</v>
+      </c>
+      <c r="D29" s="65" t="s">
+        <v>529</v>
+      </c>
+      <c r="E29" s="66" t="s">
+        <v>590</v>
+      </c>
+      <c r="F29" s="67"/>
+      <c r="G29" s="68" t="s">
+        <v>544</v>
+      </c>
+      <c r="H29" s="69" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="62" t="s">
+        <v>526</v>
+      </c>
+      <c r="B30" s="63" t="s">
+        <v>552</v>
+      </c>
+      <c r="C30" s="64" t="s">
+        <v>591</v>
+      </c>
+      <c r="D30" s="65" t="s">
+        <v>529</v>
+      </c>
+      <c r="E30" s="66" t="s">
+        <v>592</v>
+      </c>
+      <c r="F30" s="67"/>
+      <c r="G30" s="68" t="s">
         <v>531</v>
       </c>
-      <c r="H9" s="0" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="H30" s="69" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="62" t="s">
         <v>526</v>
       </c>
-      <c r="B10" s="0" t="s">
-        <v>527</v>
-      </c>
-      <c r="C10" s="0" t="s">
-        <v>549</v>
-      </c>
-      <c r="D10" s="0" t="s">
+      <c r="B31" s="63" t="s">
+        <v>552</v>
+      </c>
+      <c r="C31" s="64" t="s">
+        <v>593</v>
+      </c>
+      <c r="D31" s="65" t="s">
         <v>529</v>
       </c>
-      <c r="E10" s="0" t="s">
-        <v>550</v>
-      </c>
-      <c r="G10" s="0" t="s">
-        <v>543</v>
-      </c>
-      <c r="H10" s="0" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="E31" s="66" t="s">
+        <v>594</v>
+      </c>
+      <c r="F31" s="67"/>
+      <c r="G31" s="68" t="s">
+        <v>544</v>
+      </c>
+      <c r="H31" s="69" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="62" t="s">
         <v>526</v>
       </c>
-      <c r="B11" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C11" s="0" t="s">
+      <c r="B32" s="63" t="s">
         <v>552</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="C32" s="64" t="s">
+        <v>595</v>
+      </c>
+      <c r="D32" s="65" t="s">
         <v>529</v>
       </c>
-      <c r="E11" s="0" t="s">
-        <v>553</v>
-      </c>
-      <c r="G11" s="0" t="s">
-        <v>546</v>
-      </c>
-      <c r="H11" s="0" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>526</v>
-      </c>
-      <c r="B12" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C12" s="0" t="s">
-        <v>554</v>
-      </c>
-      <c r="D12" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E12" s="0" t="s">
-        <v>555</v>
-      </c>
-      <c r="G12" s="0" t="s">
-        <v>538</v>
-      </c>
-      <c r="H12" s="0" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>526</v>
-      </c>
-      <c r="B13" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C13" s="0" t="s">
-        <v>556</v>
-      </c>
-      <c r="D13" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E13" s="0" t="s">
-        <v>557</v>
-      </c>
-      <c r="G13" s="0" t="s">
-        <v>538</v>
-      </c>
-      <c r="H13" s="0" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
-        <v>526</v>
-      </c>
-      <c r="B14" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C14" s="0" t="s">
-        <v>558</v>
-      </c>
-      <c r="D14" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E14" s="0" t="s">
-        <v>559</v>
-      </c>
-      <c r="G14" s="0" t="s">
-        <v>543</v>
-      </c>
-      <c r="H14" s="0" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
-        <v>526</v>
-      </c>
-      <c r="B15" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C15" s="0" t="s">
-        <v>560</v>
-      </c>
-      <c r="D15" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E15" s="0" t="s">
-        <v>561</v>
-      </c>
-      <c r="G15" s="0" t="s">
-        <v>535</v>
-      </c>
-      <c r="H15" s="0" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
-        <v>526</v>
-      </c>
-      <c r="B16" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C16" s="0" t="s">
-        <v>562</v>
-      </c>
-      <c r="D16" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E16" s="0" t="s">
-        <v>563</v>
-      </c>
-      <c r="G16" s="0" t="s">
+      <c r="E32" s="66" t="s">
+        <v>596</v>
+      </c>
+      <c r="F32" s="67"/>
+      <c r="G32" s="68" t="s">
         <v>531</v>
       </c>
-      <c r="H16" s="0" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
-        <v>526</v>
-      </c>
-      <c r="B17" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C17" s="0" t="s">
-        <v>564</v>
-      </c>
-      <c r="D17" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E17" s="0" t="s">
-        <v>565</v>
-      </c>
-      <c r="G17" s="0" t="s">
-        <v>546</v>
-      </c>
-      <c r="H17" s="0" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
-        <v>526</v>
-      </c>
-      <c r="B18" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C18" s="0" t="s">
-        <v>567</v>
-      </c>
-      <c r="D18" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E18" s="0" t="s">
-        <v>568</v>
-      </c>
-      <c r="G18" s="0" t="s">
-        <v>538</v>
-      </c>
-      <c r="H18" s="0" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
-        <v>526</v>
-      </c>
-      <c r="B19" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C19" s="0" t="s">
-        <v>569</v>
-      </c>
-      <c r="D19" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E19" s="0" t="s">
-        <v>570</v>
-      </c>
-      <c r="G19" s="0" t="s">
-        <v>546</v>
-      </c>
-      <c r="H19" s="0" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>526</v>
-      </c>
-      <c r="B20" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C20" s="0" t="s">
-        <v>571</v>
-      </c>
-      <c r="D20" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E20" s="0" t="s">
-        <v>572</v>
-      </c>
-      <c r="G20" s="0" t="s">
-        <v>538</v>
-      </c>
-      <c r="H20" s="0" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
-        <v>526</v>
-      </c>
-      <c r="B21" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C21" s="0" t="s">
-        <v>573</v>
-      </c>
-      <c r="D21" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E21" s="0" t="s">
-        <v>574</v>
-      </c>
-      <c r="G21" s="0" t="s">
-        <v>546</v>
-      </c>
-      <c r="H21" s="0" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
-        <v>526</v>
-      </c>
-      <c r="B22" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C22" s="0" t="s">
-        <v>575</v>
-      </c>
-      <c r="D22" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E22" s="0" t="s">
-        <v>576</v>
-      </c>
-      <c r="G22" s="0" t="s">
-        <v>535</v>
-      </c>
-      <c r="H22" s="0" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
-        <v>526</v>
-      </c>
-      <c r="B23" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C23" s="0" t="s">
-        <v>577</v>
-      </c>
-      <c r="D23" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E23" s="0" t="s">
-        <v>578</v>
-      </c>
-      <c r="G23" s="0" t="s">
-        <v>531</v>
-      </c>
-      <c r="H23" s="0" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
-        <v>526</v>
-      </c>
-      <c r="B24" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C24" s="0" t="s">
-        <v>579</v>
-      </c>
-      <c r="D24" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E24" s="0" t="s">
-        <v>580</v>
-      </c>
-      <c r="G24" s="0" t="s">
-        <v>543</v>
-      </c>
-      <c r="H24" s="0" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
-        <v>526</v>
-      </c>
-      <c r="B25" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C25" s="0" t="s">
-        <v>581</v>
-      </c>
-      <c r="D25" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E25" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="G25" s="0" t="s">
-        <v>535</v>
-      </c>
-      <c r="H25" s="0" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
-        <v>526</v>
-      </c>
-      <c r="B26" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C26" s="0" t="s">
-        <v>583</v>
-      </c>
-      <c r="D26" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E26" s="0" t="s">
-        <v>584</v>
-      </c>
-      <c r="G26" s="0" t="s">
-        <v>546</v>
-      </c>
-      <c r="H26" s="0" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
-        <v>526</v>
-      </c>
-      <c r="B27" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C27" s="0" t="s">
-        <v>585</v>
-      </c>
-      <c r="D27" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E27" s="0" t="s">
-        <v>586</v>
-      </c>
-      <c r="G27" s="0" t="s">
-        <v>535</v>
-      </c>
-      <c r="H27" s="0" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
-        <v>526</v>
-      </c>
-      <c r="B28" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C28" s="0" t="s">
-        <v>587</v>
-      </c>
-      <c r="D28" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E28" s="0" t="s">
-        <v>588</v>
-      </c>
-      <c r="G28" s="0" t="s">
-        <v>538</v>
-      </c>
-      <c r="H28" s="0" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
-        <v>526</v>
-      </c>
-      <c r="B29" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C29" s="0" t="s">
-        <v>589</v>
-      </c>
-      <c r="D29" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E29" s="0" t="s">
-        <v>590</v>
-      </c>
-      <c r="G29" s="0" t="s">
-        <v>543</v>
-      </c>
-      <c r="H29" s="0" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
-        <v>526</v>
-      </c>
-      <c r="B30" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C30" s="0" t="s">
-        <v>591</v>
-      </c>
-      <c r="D30" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E30" s="0" t="s">
-        <v>592</v>
-      </c>
-      <c r="G30" s="0" t="s">
-        <v>531</v>
-      </c>
-      <c r="H30" s="0" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
-        <v>526</v>
-      </c>
-      <c r="B31" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C31" s="0" t="s">
-        <v>593</v>
-      </c>
-      <c r="D31" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E31" s="0" t="s">
-        <v>594</v>
-      </c>
-      <c r="G31" s="0" t="s">
-        <v>543</v>
-      </c>
-      <c r="H31" s="0" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
-        <v>526</v>
-      </c>
-      <c r="B32" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C32" s="0" t="s">
-        <v>595</v>
-      </c>
-      <c r="D32" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E32" s="0" t="s">
-        <v>596</v>
-      </c>
-      <c r="G32" s="0" t="s">
-        <v>531</v>
-      </c>
-      <c r="H32" s="0" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B33" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C33" s="0" t="s">
-        <v>598</v>
-      </c>
-      <c r="D33" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E33" s="0" t="s">
-        <v>599</v>
-      </c>
-      <c r="G33" s="0" t="s">
-        <v>600</v>
-      </c>
-      <c r="H33" s="0" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B34" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C34" s="0" t="s">
-        <v>602</v>
-      </c>
-      <c r="D34" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E34" s="0" t="s">
-        <v>603</v>
-      </c>
-      <c r="G34" s="0" t="s">
-        <v>604</v>
-      </c>
-      <c r="H34" s="0" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B35" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C35" s="0" t="s">
-        <v>605</v>
-      </c>
-      <c r="D35" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E35" s="0" t="s">
-        <v>606</v>
-      </c>
-      <c r="G35" s="0" t="s">
-        <v>607</v>
-      </c>
-      <c r="H35" s="0" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B36" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C36" s="0" t="s">
-        <v>608</v>
-      </c>
-      <c r="D36" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E36" s="0" t="s">
-        <v>609</v>
-      </c>
-      <c r="G36" s="0" t="s">
-        <v>604</v>
-      </c>
-      <c r="H36" s="0" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B37" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C37" s="0" t="s">
-        <v>610</v>
-      </c>
-      <c r="D37" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E37" s="0" t="s">
-        <v>611</v>
-      </c>
-      <c r="G37" s="0" t="s">
-        <v>612</v>
-      </c>
-      <c r="H37" s="0" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B38" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C38" s="0" t="s">
-        <v>613</v>
-      </c>
-      <c r="D38" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E38" s="0" t="s">
-        <v>614</v>
-      </c>
-      <c r="G38" s="0" t="s">
-        <v>615</v>
-      </c>
-      <c r="H38" s="0" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B39" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C39" s="0" t="s">
-        <v>616</v>
-      </c>
-      <c r="D39" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E39" s="0" t="s">
-        <v>617</v>
-      </c>
-      <c r="G39" s="0" t="s">
-        <v>600</v>
-      </c>
-      <c r="H39" s="0" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B40" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C40" s="0" t="s">
-        <v>618</v>
-      </c>
-      <c r="D40" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E40" s="0" t="s">
-        <v>619</v>
-      </c>
-      <c r="G40" s="0" t="s">
-        <v>612</v>
-      </c>
-      <c r="H40" s="0" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B41" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C41" s="0" t="s">
-        <v>620</v>
-      </c>
-      <c r="D41" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E41" s="0" t="s">
-        <v>621</v>
-      </c>
-      <c r="G41" s="0" t="s">
-        <v>615</v>
-      </c>
-      <c r="H41" s="0" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B42" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C42" s="0" t="s">
-        <v>622</v>
-      </c>
-      <c r="D42" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E42" s="0" t="s">
-        <v>623</v>
-      </c>
-      <c r="G42" s="0" t="s">
-        <v>607</v>
-      </c>
-      <c r="H42" s="0" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B43" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C43" s="0" t="s">
-        <v>624</v>
-      </c>
-      <c r="D43" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E43" s="0" t="s">
-        <v>625</v>
-      </c>
-      <c r="G43" s="0" t="s">
-        <v>607</v>
-      </c>
-      <c r="H43" s="0" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B44" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C44" s="0" t="s">
-        <v>626</v>
-      </c>
-      <c r="D44" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E44" s="0" t="s">
-        <v>627</v>
-      </c>
-      <c r="G44" s="0" t="s">
-        <v>612</v>
-      </c>
-      <c r="H44" s="0" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B45" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C45" s="0" t="s">
-        <v>628</v>
-      </c>
-      <c r="D45" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E45" s="0" t="s">
-        <v>629</v>
-      </c>
-      <c r="G45" s="0" t="s">
-        <v>604</v>
-      </c>
-      <c r="H45" s="0" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B46" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C46" s="0" t="s">
-        <v>630</v>
-      </c>
-      <c r="D46" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E46" s="0" t="s">
-        <v>631</v>
-      </c>
-      <c r="G46" s="0" t="s">
-        <v>600</v>
-      </c>
-      <c r="H46" s="0" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B47" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C47" s="0" t="s">
-        <v>632</v>
-      </c>
-      <c r="D47" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E47" s="0" t="s">
-        <v>633</v>
-      </c>
-      <c r="G47" s="0" t="s">
-        <v>615</v>
-      </c>
-      <c r="H47" s="0" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B48" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C48" s="0" t="s">
-        <v>634</v>
-      </c>
-      <c r="D48" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E48" s="0" t="s">
-        <v>635</v>
-      </c>
-      <c r="G48" s="0" t="s">
-        <v>607</v>
-      </c>
-      <c r="H48" s="0" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B49" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C49" s="0" t="s">
-        <v>636</v>
-      </c>
-      <c r="D49" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E49" s="0" t="s">
-        <v>637</v>
-      </c>
-      <c r="G49" s="0" t="s">
-        <v>615</v>
-      </c>
-      <c r="H49" s="0" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B50" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C50" s="0" t="s">
-        <v>638</v>
-      </c>
-      <c r="D50" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E50" s="0" t="s">
-        <v>639</v>
-      </c>
-      <c r="G50" s="0" t="s">
-        <v>607</v>
-      </c>
-      <c r="H50" s="0" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B51" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C51" s="0" t="s">
-        <v>640</v>
-      </c>
-      <c r="D51" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E51" s="0" t="s">
-        <v>641</v>
-      </c>
-      <c r="G51" s="0" t="s">
-        <v>615</v>
-      </c>
-      <c r="H51" s="0" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B52" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C52" s="0" t="s">
-        <v>642</v>
-      </c>
-      <c r="D52" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E52" s="0" t="s">
-        <v>643</v>
-      </c>
-      <c r="G52" s="0" t="s">
-        <v>604</v>
-      </c>
-      <c r="H52" s="0" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B53" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C53" s="0" t="s">
-        <v>644</v>
-      </c>
-      <c r="D53" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E53" s="0" t="s">
-        <v>645</v>
-      </c>
-      <c r="G53" s="0" t="s">
-        <v>600</v>
-      </c>
-      <c r="H53" s="0" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B54" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C54" s="0" t="s">
-        <v>646</v>
-      </c>
-      <c r="D54" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E54" s="0" t="s">
-        <v>647</v>
-      </c>
-      <c r="G54" s="0" t="s">
-        <v>612</v>
-      </c>
-      <c r="H54" s="0" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B55" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C55" s="0" t="s">
-        <v>648</v>
-      </c>
-      <c r="D55" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E55" s="0" t="s">
-        <v>649</v>
-      </c>
-      <c r="G55" s="0" t="s">
-        <v>604</v>
-      </c>
-      <c r="H55" s="0" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B56" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C56" s="0" t="s">
-        <v>650</v>
-      </c>
-      <c r="D56" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E56" s="0" t="s">
-        <v>651</v>
-      </c>
-      <c r="G56" s="0" t="s">
-        <v>615</v>
-      </c>
-      <c r="H56" s="0" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B57" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C57" s="0" t="s">
-        <v>652</v>
-      </c>
-      <c r="D57" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E57" s="0" t="s">
-        <v>653</v>
-      </c>
-      <c r="G57" s="0" t="s">
-        <v>604</v>
-      </c>
-      <c r="H57" s="0" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B58" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C58" s="0" t="s">
-        <v>654</v>
-      </c>
-      <c r="D58" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E58" s="0" t="s">
-        <v>655</v>
-      </c>
-      <c r="G58" s="0" t="s">
-        <v>607</v>
-      </c>
-      <c r="H58" s="0" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B59" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C59" s="0" t="s">
-        <v>656</v>
-      </c>
-      <c r="D59" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E59" s="0" t="s">
-        <v>657</v>
-      </c>
-      <c r="G59" s="0" t="s">
-        <v>612</v>
-      </c>
-      <c r="H59" s="0" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B60" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C60" s="0" t="s">
-        <v>658</v>
-      </c>
-      <c r="D60" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E60" s="0" t="s">
-        <v>659</v>
-      </c>
-      <c r="G60" s="0" t="s">
-        <v>600</v>
-      </c>
-      <c r="H60" s="0" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B61" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C61" s="0" t="s">
-        <v>660</v>
-      </c>
-      <c r="D61" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E61" s="0" t="s">
-        <v>661</v>
-      </c>
-      <c r="G61" s="0" t="s">
-        <v>612</v>
-      </c>
-      <c r="H61" s="0" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B62" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C62" s="0" t="s">
-        <v>662</v>
-      </c>
-      <c r="D62" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E62" s="0" t="s">
-        <v>663</v>
-      </c>
-      <c r="G62" s="0" t="s">
-        <v>600</v>
-      </c>
-      <c r="H62" s="0" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B63" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C63" s="0" t="s">
-        <v>664</v>
-      </c>
-      <c r="D63" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E63" s="0" t="s">
-        <v>665</v>
-      </c>
-      <c r="G63" s="0" t="s">
-        <v>600</v>
-      </c>
-      <c r="H63" s="0" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B64" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C64" s="0" t="s">
-        <v>667</v>
-      </c>
-      <c r="D64" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E64" s="0" t="s">
-        <v>668</v>
-      </c>
-      <c r="G64" s="0" t="s">
-        <v>604</v>
-      </c>
-      <c r="H64" s="0" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B65" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C65" s="0" t="s">
-        <v>669</v>
-      </c>
-      <c r="D65" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E65" s="0" t="s">
-        <v>670</v>
-      </c>
-      <c r="G65" s="0" t="s">
-        <v>607</v>
-      </c>
-      <c r="H65" s="0" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B66" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C66" s="0" t="s">
-        <v>671</v>
-      </c>
-      <c r="D66" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E66" s="0" t="s">
-        <v>672</v>
-      </c>
-      <c r="G66" s="0" t="s">
-        <v>604</v>
-      </c>
-      <c r="H66" s="0" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B67" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C67" s="0" t="s">
-        <v>673</v>
-      </c>
-      <c r="D67" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E67" s="0" t="s">
-        <v>674</v>
-      </c>
-      <c r="G67" s="0" t="s">
-        <v>612</v>
-      </c>
-      <c r="H67" s="0" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B68" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C68" s="0" t="s">
-        <v>675</v>
-      </c>
-      <c r="D68" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E68" s="0" t="s">
-        <v>676</v>
-      </c>
-      <c r="G68" s="0" t="s">
-        <v>615</v>
-      </c>
-      <c r="H68" s="0" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B69" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C69" s="0" t="s">
-        <v>677</v>
-      </c>
-      <c r="D69" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E69" s="0" t="s">
-        <v>678</v>
-      </c>
-      <c r="G69" s="0" t="s">
-        <v>600</v>
-      </c>
-      <c r="H69" s="0" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B70" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C70" s="0" t="s">
-        <v>679</v>
-      </c>
-      <c r="D70" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E70" s="0" t="s">
-        <v>680</v>
-      </c>
-      <c r="G70" s="0" t="s">
-        <v>612</v>
-      </c>
-      <c r="H70" s="0" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B71" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C71" s="0" t="s">
-        <v>681</v>
-      </c>
-      <c r="D71" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E71" s="0" t="s">
-        <v>682</v>
-      </c>
-      <c r="G71" s="0" t="s">
-        <v>615</v>
-      </c>
-      <c r="H71" s="0" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B72" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C72" s="0" t="s">
-        <v>683</v>
-      </c>
-      <c r="D72" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E72" s="0" t="s">
-        <v>684</v>
-      </c>
-      <c r="G72" s="0" t="s">
-        <v>607</v>
-      </c>
-      <c r="H72" s="0" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B73" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C73" s="0" t="s">
-        <v>685</v>
-      </c>
-      <c r="D73" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E73" s="0" t="s">
-        <v>686</v>
-      </c>
-      <c r="G73" s="0" t="s">
-        <v>607</v>
-      </c>
-      <c r="H73" s="0" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B74" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C74" s="0" t="s">
-        <v>687</v>
-      </c>
-      <c r="D74" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E74" s="0" t="s">
-        <v>688</v>
-      </c>
-      <c r="G74" s="0" t="s">
-        <v>612</v>
-      </c>
-      <c r="H74" s="0" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B75" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C75" s="0" t="s">
-        <v>689</v>
-      </c>
-      <c r="D75" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E75" s="0" t="s">
-        <v>690</v>
-      </c>
-      <c r="G75" s="0" t="s">
-        <v>604</v>
-      </c>
-      <c r="H75" s="0" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B76" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C76" s="0" t="s">
-        <v>691</v>
-      </c>
-      <c r="D76" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E76" s="0" t="s">
-        <v>692</v>
-      </c>
-      <c r="G76" s="0" t="s">
-        <v>600</v>
-      </c>
-      <c r="H76" s="0" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B77" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C77" s="0" t="s">
-        <v>693</v>
-      </c>
-      <c r="D77" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E77" s="0" t="s">
-        <v>694</v>
-      </c>
-      <c r="G77" s="0" t="s">
-        <v>615</v>
-      </c>
-      <c r="H77" s="0" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B78" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C78" s="0" t="s">
-        <v>695</v>
-      </c>
-      <c r="D78" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E78" s="0" t="s">
-        <v>696</v>
-      </c>
-      <c r="G78" s="0" t="s">
-        <v>607</v>
-      </c>
-      <c r="H78" s="0" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B79" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C79" s="0" t="s">
-        <v>697</v>
-      </c>
-      <c r="D79" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E79" s="0" t="s">
-        <v>698</v>
-      </c>
-      <c r="G79" s="0" t="s">
-        <v>615</v>
-      </c>
-      <c r="H79" s="0" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B80" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C80" s="0" t="s">
-        <v>699</v>
-      </c>
-      <c r="D80" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E80" s="0" t="s">
-        <v>700</v>
-      </c>
-      <c r="G80" s="0" t="s">
-        <v>607</v>
-      </c>
-      <c r="H80" s="0" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B81" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C81" s="0" t="s">
-        <v>701</v>
-      </c>
-      <c r="D81" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E81" s="0" t="s">
-        <v>702</v>
-      </c>
-      <c r="G81" s="0" t="s">
-        <v>615</v>
-      </c>
-      <c r="H81" s="0" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B82" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C82" s="0" t="s">
-        <v>703</v>
-      </c>
-      <c r="D82" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E82" s="0" t="s">
-        <v>704</v>
-      </c>
-      <c r="G82" s="0" t="s">
-        <v>604</v>
-      </c>
-      <c r="H82" s="0" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B83" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C83" s="0" t="s">
-        <v>706</v>
-      </c>
-      <c r="D83" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E83" s="0" t="s">
-        <v>707</v>
-      </c>
-      <c r="G83" s="0" t="s">
-        <v>600</v>
-      </c>
-      <c r="H83" s="0" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B84" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C84" s="0" t="s">
-        <v>708</v>
-      </c>
-      <c r="D84" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E84" s="0" t="s">
-        <v>709</v>
-      </c>
-      <c r="G84" s="0" t="s">
-        <v>612</v>
-      </c>
-      <c r="H84" s="0" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B85" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C85" s="0" t="s">
-        <v>710</v>
-      </c>
-      <c r="D85" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E85" s="0" t="s">
-        <v>711</v>
-      </c>
-      <c r="G85" s="0" t="s">
-        <v>604</v>
-      </c>
-      <c r="H85" s="0" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B86" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C86" s="0" t="s">
-        <v>712</v>
-      </c>
-      <c r="D86" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E86" s="0" t="s">
-        <v>713</v>
-      </c>
-      <c r="G86" s="0" t="s">
-        <v>615</v>
-      </c>
-      <c r="H86" s="0" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B87" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C87" s="0" t="s">
-        <v>714</v>
-      </c>
-      <c r="D87" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E87" s="0" t="s">
-        <v>715</v>
-      </c>
-      <c r="G87" s="0" t="s">
-        <v>604</v>
-      </c>
-      <c r="H87" s="0" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B88" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C88" s="0" t="s">
-        <v>716</v>
-      </c>
-      <c r="D88" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E88" s="0" t="s">
-        <v>717</v>
-      </c>
-      <c r="G88" s="0" t="s">
-        <v>607</v>
-      </c>
-      <c r="H88" s="0" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B89" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C89" s="0" t="s">
-        <v>718</v>
-      </c>
-      <c r="D89" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E89" s="0" t="s">
-        <v>719</v>
-      </c>
-      <c r="G89" s="0" t="s">
-        <v>612</v>
-      </c>
-      <c r="H89" s="0" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B90" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C90" s="0" t="s">
-        <v>720</v>
-      </c>
-      <c r="D90" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E90" s="0" t="s">
-        <v>721</v>
-      </c>
-      <c r="G90" s="0" t="s">
-        <v>600</v>
-      </c>
-      <c r="H90" s="0" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B91" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C91" s="0" t="s">
-        <v>722</v>
-      </c>
-      <c r="D91" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E91" s="0" t="s">
-        <v>723</v>
-      </c>
-      <c r="G91" s="0" t="s">
-        <v>612</v>
-      </c>
-      <c r="H91" s="0" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B92" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C92" s="0" t="s">
-        <v>724</v>
-      </c>
-      <c r="D92" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E92" s="0" t="s">
-        <v>725</v>
-      </c>
-      <c r="G92" s="0" t="s">
-        <v>600</v>
-      </c>
-      <c r="H92" s="0" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B93" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C93" s="0" t="s">
-        <v>726</v>
-      </c>
-      <c r="D93" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E93" s="0" t="s">
-        <v>727</v>
-      </c>
-      <c r="G93" s="0" t="s">
-        <v>600</v>
-      </c>
-      <c r="H93" s="0" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B94" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C94" s="0" t="s">
-        <v>729</v>
-      </c>
-      <c r="D94" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E94" s="0" t="s">
-        <v>730</v>
-      </c>
-      <c r="G94" s="0" t="s">
-        <v>604</v>
-      </c>
-      <c r="H94" s="0" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B95" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C95" s="0" t="s">
-        <v>731</v>
-      </c>
-      <c r="D95" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E95" s="0" t="s">
-        <v>732</v>
-      </c>
-      <c r="G95" s="0" t="s">
-        <v>607</v>
-      </c>
-      <c r="H95" s="0" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B96" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C96" s="0" t="s">
-        <v>733</v>
-      </c>
-      <c r="D96" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E96" s="0" t="s">
-        <v>734</v>
-      </c>
-      <c r="G96" s="0" t="s">
-        <v>604</v>
-      </c>
-      <c r="H96" s="0" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B97" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C97" s="0" t="s">
-        <v>735</v>
-      </c>
-      <c r="D97" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E97" s="0" t="s">
-        <v>736</v>
-      </c>
-      <c r="G97" s="0" t="s">
-        <v>612</v>
-      </c>
-      <c r="H97" s="0" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B98" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C98" s="0" t="s">
-        <v>737</v>
-      </c>
-      <c r="D98" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E98" s="0" t="s">
-        <v>738</v>
-      </c>
-      <c r="G98" s="0" t="s">
-        <v>615</v>
-      </c>
-      <c r="H98" s="0" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B99" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C99" s="0" t="s">
-        <v>739</v>
-      </c>
-      <c r="D99" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E99" s="0" t="s">
-        <v>740</v>
-      </c>
-      <c r="G99" s="0" t="s">
-        <v>600</v>
-      </c>
-      <c r="H99" s="0" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B100" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C100" s="0" t="s">
-        <v>741</v>
-      </c>
-      <c r="D100" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E100" s="0" t="s">
-        <v>742</v>
-      </c>
-      <c r="G100" s="0" t="s">
-        <v>612</v>
-      </c>
-      <c r="H100" s="0" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B101" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C101" s="0" t="s">
-        <v>743</v>
-      </c>
-      <c r="D101" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E101" s="0" t="s">
-        <v>744</v>
-      </c>
-      <c r="G101" s="0" t="s">
-        <v>615</v>
-      </c>
-      <c r="H101" s="0" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B102" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C102" s="0" t="s">
-        <v>745</v>
-      </c>
-      <c r="D102" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E102" s="0" t="s">
-        <v>746</v>
-      </c>
-      <c r="G102" s="0" t="s">
-        <v>607</v>
-      </c>
-      <c r="H102" s="0" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B103" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C103" s="0" t="s">
-        <v>748</v>
-      </c>
-      <c r="D103" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E103" s="0" t="s">
-        <v>749</v>
-      </c>
-      <c r="G103" s="0" t="s">
-        <v>607</v>
-      </c>
-      <c r="H103" s="0" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B104" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C104" s="0" t="s">
-        <v>750</v>
-      </c>
-      <c r="D104" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E104" s="0" t="s">
-        <v>751</v>
-      </c>
-      <c r="G104" s="0" t="s">
-        <v>612</v>
-      </c>
-      <c r="H104" s="0" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B105" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C105" s="0" t="s">
-        <v>752</v>
-      </c>
-      <c r="D105" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E105" s="0" t="s">
-        <v>753</v>
-      </c>
-      <c r="G105" s="0" t="s">
-        <v>604</v>
-      </c>
-      <c r="H105" s="0" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B106" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C106" s="0" t="s">
-        <v>754</v>
-      </c>
-      <c r="D106" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E106" s="0" t="s">
-        <v>755</v>
-      </c>
-      <c r="G106" s="0" t="s">
-        <v>600</v>
-      </c>
-      <c r="H106" s="0" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B107" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C107" s="0" t="s">
-        <v>756</v>
-      </c>
-      <c r="D107" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E107" s="0" t="s">
-        <v>757</v>
-      </c>
-      <c r="G107" s="0" t="s">
-        <v>615</v>
-      </c>
-      <c r="H107" s="0" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B108" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C108" s="0" t="s">
-        <v>758</v>
-      </c>
-      <c r="D108" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E108" s="0" t="s">
-        <v>759</v>
-      </c>
-      <c r="G108" s="0" t="s">
-        <v>607</v>
-      </c>
-      <c r="H108" s="0" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B109" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C109" s="0" t="s">
-        <v>760</v>
-      </c>
-      <c r="D109" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E109" s="0" t="s">
-        <v>761</v>
-      </c>
-      <c r="G109" s="0" t="s">
-        <v>615</v>
-      </c>
-      <c r="H109" s="0" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B110" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C110" s="0" t="s">
-        <v>762</v>
-      </c>
-      <c r="D110" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E110" s="0" t="s">
-        <v>763</v>
-      </c>
-      <c r="G110" s="0" t="s">
-        <v>607</v>
-      </c>
-      <c r="H110" s="0" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B111" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C111" s="0" t="s">
-        <v>764</v>
-      </c>
-      <c r="D111" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E111" s="0" t="s">
-        <v>765</v>
-      </c>
-      <c r="G111" s="0" t="s">
-        <v>615</v>
-      </c>
-      <c r="H111" s="0" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B112" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C112" s="0" t="s">
-        <v>766</v>
-      </c>
-      <c r="D112" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E112" s="0" t="s">
-        <v>767</v>
-      </c>
-      <c r="G112" s="0" t="s">
-        <v>604</v>
-      </c>
-      <c r="H112" s="0" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B113" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C113" s="0" t="s">
-        <v>768</v>
-      </c>
-      <c r="D113" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E113" s="0" t="s">
-        <v>769</v>
-      </c>
-      <c r="G113" s="0" t="s">
-        <v>600</v>
-      </c>
-      <c r="H113" s="0" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B114" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C114" s="0" t="s">
-        <v>770</v>
-      </c>
-      <c r="D114" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E114" s="0" t="s">
-        <v>771</v>
-      </c>
-      <c r="G114" s="0" t="s">
-        <v>612</v>
-      </c>
-      <c r="H114" s="0" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B115" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C115" s="0" t="s">
-        <v>772</v>
-      </c>
-      <c r="D115" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E115" s="0" t="s">
-        <v>773</v>
-      </c>
-      <c r="G115" s="0" t="s">
-        <v>604</v>
-      </c>
-      <c r="H115" s="0" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B116" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C116" s="0" t="s">
-        <v>774</v>
-      </c>
-      <c r="D116" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E116" s="0" t="s">
-        <v>775</v>
-      </c>
-      <c r="G116" s="0" t="s">
-        <v>615</v>
-      </c>
-      <c r="H116" s="0" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B117" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C117" s="0" t="s">
-        <v>776</v>
-      </c>
-      <c r="D117" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E117" s="0" t="s">
-        <v>777</v>
-      </c>
-      <c r="G117" s="0" t="s">
-        <v>604</v>
-      </c>
-      <c r="H117" s="0" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B118" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C118" s="0" t="s">
-        <v>778</v>
-      </c>
-      <c r="D118" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E118" s="0" t="s">
-        <v>779</v>
-      </c>
-      <c r="G118" s="0" t="s">
-        <v>607</v>
-      </c>
-      <c r="H118" s="0" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B119" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C119" s="0" t="s">
-        <v>780</v>
-      </c>
-      <c r="D119" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E119" s="0" t="s">
-        <v>781</v>
-      </c>
-      <c r="G119" s="0" t="s">
-        <v>612</v>
-      </c>
-      <c r="H119" s="0" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B120" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C120" s="0" t="s">
-        <v>782</v>
-      </c>
-      <c r="D120" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E120" s="0" t="s">
-        <v>783</v>
-      </c>
-      <c r="G120" s="0" t="s">
-        <v>600</v>
-      </c>
-      <c r="H120" s="0" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B121" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C121" s="0" t="s">
-        <v>784</v>
-      </c>
-      <c r="D121" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E121" s="0" t="s">
-        <v>785</v>
-      </c>
-      <c r="G121" s="0" t="s">
-        <v>612</v>
-      </c>
-      <c r="H121" s="0" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="B122" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="C122" s="0" t="s">
-        <v>786</v>
-      </c>
-      <c r="D122" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="E122" s="0" t="s">
-        <v>787</v>
-      </c>
-      <c r="G122" s="0" t="s">
-        <v>600</v>
-      </c>
-      <c r="H122" s="0" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="62" t="s">
-        <v>788</v>
-      </c>
-      <c r="B123" s="63" t="s">
-        <v>527</v>
-      </c>
-      <c r="C123" s="64" t="s">
-        <v>789</v>
-      </c>
-      <c r="D123" s="65" t="s">
-        <v>529</v>
-      </c>
-      <c r="E123" s="66" t="s">
-        <v>790</v>
-      </c>
-      <c r="F123" s="67"/>
-      <c r="G123" s="68" t="s">
-        <v>791</v>
-      </c>
-      <c r="H123" s="69" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="62" t="s">
-        <v>788</v>
-      </c>
-      <c r="B124" s="63" t="s">
-        <v>527</v>
-      </c>
-      <c r="C124" s="64" t="s">
-        <v>793</v>
-      </c>
-      <c r="D124" s="65" t="s">
-        <v>529</v>
-      </c>
-      <c r="E124" s="66" t="s">
-        <v>794</v>
-      </c>
-      <c r="F124" s="67"/>
-      <c r="G124" s="68" t="s">
-        <v>795</v>
-      </c>
-      <c r="H124" s="69" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="62" t="s">
-        <v>788</v>
-      </c>
-      <c r="B125" s="63" t="s">
-        <v>527</v>
-      </c>
-      <c r="C125" s="64" t="s">
-        <v>796</v>
-      </c>
-      <c r="D125" s="65" t="s">
-        <v>529</v>
-      </c>
-      <c r="E125" s="66" t="s">
-        <v>797</v>
-      </c>
-      <c r="F125" s="67"/>
-      <c r="G125" s="68" t="s">
-        <v>798</v>
-      </c>
-      <c r="H125" s="69" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="62" t="s">
-        <v>788</v>
-      </c>
-      <c r="B126" s="63" t="s">
-        <v>527</v>
-      </c>
-      <c r="C126" s="64" t="s">
-        <v>800</v>
-      </c>
-      <c r="D126" s="65" t="s">
-        <v>529</v>
-      </c>
-      <c r="E126" s="66" t="s">
-        <v>801</v>
-      </c>
-      <c r="F126" s="67"/>
-      <c r="G126" s="68" t="s">
-        <v>795</v>
-      </c>
-      <c r="H126" s="69" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="62" t="s">
-        <v>788</v>
-      </c>
-      <c r="B127" s="63" t="s">
-        <v>527</v>
-      </c>
-      <c r="C127" s="64" t="s">
-        <v>802</v>
-      </c>
-      <c r="D127" s="65" t="s">
-        <v>529</v>
-      </c>
-      <c r="E127" s="66" t="s">
-        <v>803</v>
-      </c>
-      <c r="F127" s="67"/>
-      <c r="G127" s="68" t="s">
-        <v>804</v>
-      </c>
-      <c r="H127" s="69" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="62" t="s">
-        <v>788</v>
-      </c>
-      <c r="B128" s="63" t="s">
-        <v>527</v>
-      </c>
-      <c r="C128" s="64" t="s">
-        <v>805</v>
-      </c>
-      <c r="D128" s="65" t="s">
-        <v>529</v>
-      </c>
-      <c r="E128" s="66" t="s">
-        <v>806</v>
-      </c>
-      <c r="F128" s="67"/>
-      <c r="G128" s="68" t="s">
-        <v>807</v>
-      </c>
-      <c r="H128" s="69" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="62" t="s">
-        <v>788</v>
-      </c>
-      <c r="B129" s="63" t="s">
-        <v>527</v>
-      </c>
-      <c r="C129" s="64" t="s">
-        <v>808</v>
-      </c>
-      <c r="D129" s="65" t="s">
-        <v>529</v>
-      </c>
-      <c r="E129" s="66" t="s">
-        <v>809</v>
-      </c>
-      <c r="F129" s="67"/>
-      <c r="G129" s="68" t="s">
-        <v>791</v>
-      </c>
-      <c r="H129" s="69" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="62" t="s">
-        <v>788</v>
-      </c>
-      <c r="B130" s="63" t="s">
-        <v>527</v>
-      </c>
-      <c r="C130" s="64" t="s">
-        <v>810</v>
-      </c>
-      <c r="D130" s="65" t="s">
-        <v>529</v>
-      </c>
-      <c r="E130" s="66" t="s">
-        <v>811</v>
-      </c>
-      <c r="F130" s="67"/>
-      <c r="G130" s="68" t="s">
-        <v>804</v>
-      </c>
-      <c r="H130" s="69" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="62" t="s">
-        <v>788</v>
-      </c>
-      <c r="B131" s="63" t="s">
-        <v>551</v>
-      </c>
-      <c r="C131" s="64" t="s">
-        <v>812</v>
-      </c>
-      <c r="D131" s="65" t="s">
-        <v>529</v>
-      </c>
-      <c r="E131" s="66" t="s">
-        <v>813</v>
-      </c>
-      <c r="F131" s="67"/>
-      <c r="G131" s="68" t="s">
-        <v>807</v>
-      </c>
-      <c r="H131" s="69" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="62" t="s">
-        <v>788</v>
-      </c>
-      <c r="B132" s="63" t="s">
-        <v>551</v>
-      </c>
-      <c r="C132" s="64" t="s">
-        <v>814</v>
-      </c>
-      <c r="D132" s="65" t="s">
-        <v>529</v>
-      </c>
-      <c r="E132" s="66" t="s">
-        <v>815</v>
-      </c>
-      <c r="F132" s="67"/>
-      <c r="G132" s="68" t="s">
-        <v>798</v>
-      </c>
-      <c r="H132" s="69" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="62" t="s">
-        <v>788</v>
-      </c>
-      <c r="B133" s="63" t="s">
-        <v>551</v>
-      </c>
-      <c r="C133" s="64" t="s">
-        <v>816</v>
-      </c>
-      <c r="D133" s="65" t="s">
-        <v>529</v>
-      </c>
-      <c r="E133" s="66" t="s">
-        <v>817</v>
-      </c>
-      <c r="F133" s="67"/>
-      <c r="G133" s="68" t="s">
-        <v>798</v>
-      </c>
-      <c r="H133" s="69" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="62" t="s">
-        <v>788</v>
-      </c>
-      <c r="B134" s="63" t="s">
-        <v>551</v>
-      </c>
-      <c r="C134" s="64" t="s">
-        <v>818</v>
-      </c>
-      <c r="D134" s="65" t="s">
-        <v>529</v>
-      </c>
-      <c r="E134" s="66" t="s">
-        <v>819</v>
-      </c>
-      <c r="F134" s="67"/>
-      <c r="G134" s="68" t="s">
-        <v>804</v>
-      </c>
-      <c r="H134" s="69" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="62" t="s">
-        <v>788</v>
-      </c>
-      <c r="B135" s="63" t="s">
-        <v>551</v>
-      </c>
-      <c r="C135" s="64" t="s">
-        <v>820</v>
-      </c>
-      <c r="D135" s="65" t="s">
-        <v>529</v>
-      </c>
-      <c r="E135" s="66" t="s">
-        <v>821</v>
-      </c>
-      <c r="F135" s="67"/>
-      <c r="G135" s="68" t="s">
-        <v>795</v>
-      </c>
-      <c r="H135" s="69" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="62" t="s">
-        <v>788</v>
-      </c>
-      <c r="B136" s="63" t="s">
-        <v>551</v>
-      </c>
-      <c r="C136" s="64" t="s">
-        <v>822</v>
-      </c>
-      <c r="D136" s="65" t="s">
-        <v>529</v>
-      </c>
-      <c r="E136" s="66" t="s">
-        <v>823</v>
-      </c>
-      <c r="F136" s="67"/>
-      <c r="G136" s="68" t="s">
-        <v>791</v>
-      </c>
-      <c r="H136" s="69" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="62" t="s">
-        <v>788</v>
-      </c>
-      <c r="B137" s="63" t="s">
-        <v>551</v>
-      </c>
-      <c r="C137" s="64" t="s">
-        <v>824</v>
-      </c>
-      <c r="D137" s="65" t="s">
-        <v>529</v>
-      </c>
-      <c r="E137" s="66" t="s">
-        <v>825</v>
-      </c>
-      <c r="F137" s="67"/>
-      <c r="G137" s="68" t="s">
-        <v>807</v>
-      </c>
-      <c r="H137" s="69" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="62" t="s">
-        <v>788</v>
-      </c>
-      <c r="B138" s="63" t="s">
-        <v>551</v>
-      </c>
-      <c r="C138" s="64" t="s">
-        <v>826</v>
-      </c>
-      <c r="D138" s="65" t="s">
-        <v>529</v>
-      </c>
-      <c r="E138" s="66" t="s">
-        <v>827</v>
-      </c>
-      <c r="F138" s="67"/>
-      <c r="G138" s="68" t="s">
-        <v>798</v>
-      </c>
-      <c r="H138" s="69" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="62" t="s">
-        <v>788</v>
-      </c>
-      <c r="B139" s="63" t="s">
-        <v>551</v>
-      </c>
-      <c r="C139" s="64" t="s">
-        <v>828</v>
-      </c>
-      <c r="D139" s="65" t="s">
-        <v>529</v>
-      </c>
-      <c r="E139" s="66" t="s">
-        <v>829</v>
-      </c>
-      <c r="F139" s="67"/>
-      <c r="G139" s="68" t="s">
-        <v>807</v>
-      </c>
-      <c r="H139" s="69" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="62" t="s">
-        <v>788</v>
-      </c>
-      <c r="B140" s="63" t="s">
-        <v>551</v>
-      </c>
-      <c r="C140" s="64" t="s">
-        <v>830</v>
-      </c>
-      <c r="D140" s="65" t="s">
-        <v>529</v>
-      </c>
-      <c r="E140" s="66" t="s">
-        <v>831</v>
-      </c>
-      <c r="F140" s="67"/>
-      <c r="G140" s="68" t="s">
-        <v>798</v>
-      </c>
-      <c r="H140" s="69" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="62" t="s">
-        <v>788</v>
-      </c>
-      <c r="B141" s="63" t="s">
-        <v>551</v>
-      </c>
-      <c r="C141" s="64" t="s">
-        <v>832</v>
-      </c>
-      <c r="D141" s="65" t="s">
-        <v>529</v>
-      </c>
-      <c r="E141" s="66" t="s">
-        <v>833</v>
-      </c>
-      <c r="F141" s="67"/>
-      <c r="G141" s="68" t="s">
-        <v>807</v>
-      </c>
-      <c r="H141" s="69" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="62" t="s">
-        <v>788</v>
-      </c>
-      <c r="B142" s="63" t="s">
-        <v>551</v>
-      </c>
-      <c r="C142" s="64" t="s">
-        <v>834</v>
-      </c>
-      <c r="D142" s="65" t="s">
-        <v>529</v>
-      </c>
-      <c r="E142" s="66" t="s">
-        <v>835</v>
-      </c>
-      <c r="F142" s="67"/>
-      <c r="G142" s="68" t="s">
-        <v>795</v>
-      </c>
-      <c r="H142" s="69" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="62" t="s">
-        <v>788</v>
-      </c>
-      <c r="B143" s="63" t="s">
-        <v>551</v>
-      </c>
-      <c r="C143" s="64" t="s">
-        <v>836</v>
-      </c>
-      <c r="D143" s="65" t="s">
-        <v>529</v>
-      </c>
-      <c r="E143" s="66" t="s">
-        <v>837</v>
-      </c>
-      <c r="F143" s="67"/>
-      <c r="G143" s="68" t="s">
-        <v>791</v>
-      </c>
-      <c r="H143" s="69" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="62" t="s">
-        <v>788</v>
-      </c>
-      <c r="B144" s="63" t="s">
-        <v>551</v>
-      </c>
-      <c r="C144" s="64" t="s">
-        <v>838</v>
-      </c>
-      <c r="D144" s="65" t="s">
-        <v>529</v>
-      </c>
-      <c r="E144" s="66" t="s">
-        <v>839</v>
-      </c>
-      <c r="F144" s="67"/>
-      <c r="G144" s="68" t="s">
-        <v>804</v>
-      </c>
-      <c r="H144" s="69" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="62" t="s">
-        <v>788</v>
-      </c>
-      <c r="B145" s="63" t="s">
-        <v>551</v>
-      </c>
-      <c r="C145" s="64" t="s">
-        <v>840</v>
-      </c>
-      <c r="D145" s="65" t="s">
-        <v>529</v>
-      </c>
-      <c r="E145" s="66" t="s">
-        <v>841</v>
-      </c>
-      <c r="F145" s="67"/>
-      <c r="G145" s="68" t="s">
-        <v>795</v>
-      </c>
-      <c r="H145" s="69" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="62" t="s">
-        <v>788</v>
-      </c>
-      <c r="B146" s="63" t="s">
-        <v>551</v>
-      </c>
-      <c r="C146" s="64" t="s">
-        <v>842</v>
-      </c>
-      <c r="D146" s="65" t="s">
-        <v>529</v>
-      </c>
-      <c r="E146" s="66" t="s">
-        <v>843</v>
-      </c>
-      <c r="F146" s="67"/>
-      <c r="G146" s="68" t="s">
-        <v>807</v>
-      </c>
-      <c r="H146" s="69" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="62" t="s">
-        <v>788</v>
-      </c>
-      <c r="B147" s="63" t="s">
-        <v>551</v>
-      </c>
-      <c r="C147" s="64" t="s">
-        <v>844</v>
-      </c>
-      <c r="D147" s="65" t="s">
-        <v>529</v>
-      </c>
-      <c r="E147" s="66" t="s">
-        <v>845</v>
-      </c>
-      <c r="F147" s="67"/>
-      <c r="G147" s="68" t="s">
-        <v>795</v>
-      </c>
-      <c r="H147" s="69" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="62" t="s">
-        <v>788</v>
-      </c>
-      <c r="B148" s="63" t="s">
-        <v>551</v>
-      </c>
-      <c r="C148" s="64" t="s">
-        <v>846</v>
-      </c>
-      <c r="D148" s="65" t="s">
-        <v>529</v>
-      </c>
-      <c r="E148" s="66" t="s">
-        <v>847</v>
-      </c>
-      <c r="F148" s="67"/>
-      <c r="G148" s="68" t="s">
-        <v>798</v>
-      </c>
-      <c r="H148" s="69" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="62" t="s">
-        <v>788</v>
-      </c>
-      <c r="B149" s="63" t="s">
-        <v>551</v>
-      </c>
-      <c r="C149" s="64" t="s">
-        <v>848</v>
-      </c>
-      <c r="D149" s="65" t="s">
-        <v>529</v>
-      </c>
-      <c r="E149" s="66" t="s">
-        <v>849</v>
-      </c>
-      <c r="F149" s="67"/>
-      <c r="G149" s="68" t="s">
-        <v>804</v>
-      </c>
-      <c r="H149" s="69" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="62" t="s">
-        <v>788</v>
-      </c>
-      <c r="B150" s="63" t="s">
-        <v>551</v>
-      </c>
-      <c r="C150" s="64" t="s">
-        <v>850</v>
-      </c>
-      <c r="D150" s="65" t="s">
-        <v>529</v>
-      </c>
-      <c r="E150" s="66" t="s">
-        <v>851</v>
-      </c>
-      <c r="F150" s="67"/>
-      <c r="G150" s="68" t="s">
-        <v>791</v>
-      </c>
-      <c r="H150" s="69" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="62" t="s">
-        <v>788</v>
-      </c>
-      <c r="B151" s="63" t="s">
-        <v>551</v>
-      </c>
-      <c r="C151" s="64" t="s">
-        <v>852</v>
-      </c>
-      <c r="D151" s="65" t="s">
-        <v>529</v>
-      </c>
-      <c r="E151" s="66" t="s">
-        <v>853</v>
-      </c>
-      <c r="F151" s="67"/>
-      <c r="G151" s="68" t="s">
-        <v>804</v>
-      </c>
-      <c r="H151" s="69" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="62" t="s">
-        <v>788</v>
-      </c>
-      <c r="B152" s="63" t="s">
-        <v>551</v>
-      </c>
-      <c r="C152" s="64" t="s">
-        <v>854</v>
-      </c>
-      <c r="D152" s="65" t="s">
-        <v>529</v>
-      </c>
-      <c r="E152" s="66" t="s">
-        <v>855</v>
-      </c>
-      <c r="F152" s="67"/>
-      <c r="G152" s="68" t="s">
-        <v>791</v>
-      </c>
-      <c r="H152" s="69" t="s">
-        <v>799</v>
-      </c>
-    </row>
+      <c r="H32" s="69" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="1048457" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048458" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048459" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048460" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048461" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048462" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048463" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048464" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048465" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048466" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048467" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048468" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048469" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048470" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048471" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048472" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048473" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048474" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048475" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048476" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048477" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048478" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048479" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048480" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048481" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048482" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048483" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048484" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048485" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048486" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048487" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048488" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048489" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048490" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048491" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048492" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048493" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048494" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048495" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048496" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048497" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048498" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048499" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048500" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048501" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048502" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048503" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048504" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048505" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048506" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048507" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048508" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048509" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048510" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048511" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048512" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048513" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048514" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048515" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048516" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048517" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048518" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048519" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048520" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048521" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048522" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048523" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048524" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048525" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048526" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048527" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048528" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048529" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048530" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048531" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048532" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048533" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048534" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048535" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048536" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048537" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048538" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048539" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048540" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048541" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048542" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048543" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048544" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048545" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048546" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048547" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048548" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048549" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048550" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048551" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048552" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048553" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048554" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048555" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048556" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048557" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048558" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048560" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -16893,7 +13476,7 @@
         <v>285</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>856</v>
+        <v>597</v>
       </c>
       <c r="F1" s="70"/>
       <c r="G1" s="70"/>
@@ -16926,7 +13509,7 @@
         <v>447</v>
       </c>
       <c r="D2" s="47" t="s">
-        <v>857</v>
+        <v>598</v>
       </c>
       <c r="E2" s="47"/>
       <c r="F2" s="72"/>
@@ -16943,13 +13526,13 @@
         <v>491</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>858</v>
+        <v>599</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>859</v>
+        <v>600</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>860</v>
+        <v>601</v>
       </c>
       <c r="E3" s="42"/>
       <c r="F3" s="72"/>
@@ -16964,13 +13547,13 @@
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="42"/>
       <c r="B4" s="1" t="s">
-        <v>861</v>
+        <v>602</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>862</v>
+        <v>603</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>863</v>
+        <v>604</v>
       </c>
       <c r="E4" s="42"/>
       <c r="F4" s="72"/>
@@ -16985,13 +13568,13 @@
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="42"/>
       <c r="B5" s="1" t="s">
-        <v>864</v>
+        <v>605</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>865</v>
+        <v>606</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>866</v>
+        <v>607</v>
       </c>
       <c r="E5" s="42"/>
       <c r="F5" s="72"/>
@@ -18069,10 +14652,10 @@
         <v>491</v>
       </c>
       <c r="B3" s="42" t="s">
-        <v>867</v>
+        <v>608</v>
       </c>
       <c r="C3" s="42" t="s">
-        <v>868</v>
+        <v>609</v>
       </c>
       <c r="D3" s="42"/>
     </row>
@@ -19174,13 +15757,13 @@
         <v>404</v>
       </c>
       <c r="R1" s="60" t="s">
-        <v>869</v>
+        <v>610</v>
       </c>
       <c r="S1" s="60" t="s">
-        <v>870</v>
+        <v>611</v>
       </c>
       <c r="T1" s="60" t="s">
-        <v>871</v>
+        <v>612</v>
       </c>
       <c r="U1" s="8"/>
       <c r="V1" s="8"/>
@@ -19191,7 +15774,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C3" s="8" t="s">
-        <v>872</v>
+        <v>613</v>
       </c>
     </row>
   </sheetData>
